--- a/04_Figures/F05_classification/MANIFEST.xlsx
+++ b/04_Figures/F05_classification/MANIFEST.xlsx
@@ -2086,19 +2086,19 @@
         <v>23</v>
       </c>
       <c r="H9" t="n">
-        <v>0.285714285714286</v>
+        <v>0.357142857142857</v>
       </c>
       <c r="I9" t="n">
-        <v>0.285714285714286</v>
+        <v>0.357142857142857</v>
       </c>
       <c r="J9" t="n">
-        <v>0.462686567164179</v>
+        <v>0.398009950248756</v>
       </c>
       <c r="K9" t="n">
-        <v>0.312410714285714</v>
+        <v>0.295625</v>
       </c>
       <c r="L9" t="n">
-        <v>0.274051944806005</v>
+        <v>0.26147700328391</v>
       </c>
       <c r="M9" t="b">
         <v>0</v>
@@ -2558,19 +2558,19 @@
         <v>23</v>
       </c>
       <c r="H17" t="n">
-        <v>0.142857142857143</v>
+        <v>0.178571428571429</v>
       </c>
       <c r="I17" t="n">
-        <v>0.142857142857143</v>
+        <v>0.178571428571429</v>
       </c>
       <c r="J17" t="n">
-        <v>0.606965174129353</v>
+        <v>0.587064676616915</v>
       </c>
       <c r="K17" t="n">
-        <v>0.306339285714286</v>
+        <v>0.296607142857143</v>
       </c>
       <c r="L17" t="n">
-        <v>0.271963012755683</v>
+        <v>0.26405102742189</v>
       </c>
       <c r="M17" t="b">
         <v>0</v>
@@ -3030,19 +3030,19 @@
         <v>23</v>
       </c>
       <c r="H25" t="n">
-        <v>0.446428571428571</v>
+        <v>0.107142857142857</v>
       </c>
       <c r="I25" t="n">
-        <v>0.446428571428571</v>
+        <v>0.107142857142857</v>
       </c>
       <c r="J25" t="n">
-        <v>0.258706467661692</v>
+        <v>0.810945273631841</v>
       </c>
       <c r="K25" t="n">
-        <v>0.304196428571429</v>
+        <v>0.297410714285714</v>
       </c>
       <c r="L25" t="n">
-        <v>0.24079543705373</v>
+        <v>0.234170951326558</v>
       </c>
       <c r="M25" t="b">
         <v>0</v>
@@ -3502,19 +3502,19 @@
         <v>23</v>
       </c>
       <c r="H33" t="n">
-        <v>0.357142857142857</v>
+        <v>0.285714285714286</v>
       </c>
       <c r="I33" t="n">
-        <v>0.357142857142857</v>
+        <v>0.285714285714286</v>
       </c>
       <c r="J33" t="n">
-        <v>0.338308457711443</v>
+        <v>0.393034825870647</v>
       </c>
       <c r="K33" t="n">
-        <v>0.287589285714286</v>
+        <v>0.273125</v>
       </c>
       <c r="L33" t="n">
-        <v>0.258274990779136</v>
+        <v>0.254187556547724</v>
       </c>
       <c r="M33" t="b">
         <v>0</v>
@@ -3974,19 +3974,19 @@
         <v>23</v>
       </c>
       <c r="H41" t="n">
-        <v>0.291666666666667</v>
+        <v>0.125</v>
       </c>
       <c r="I41" t="n">
-        <v>0.291666666666667</v>
+        <v>0.125</v>
       </c>
       <c r="J41" t="n">
-        <v>0.402985074626866</v>
+        <v>0.686567164179104</v>
       </c>
       <c r="K41" t="n">
-        <v>0.301145833333333</v>
+        <v>0.309791666666667</v>
       </c>
       <c r="L41" t="n">
-        <v>0.269341801147164</v>
+        <v>0.264805438701167</v>
       </c>
       <c r="M41" t="b">
         <v>0</v>
@@ -4446,19 +4446,19 @@
         <v>23</v>
       </c>
       <c r="H49" t="n">
-        <v>0.125</v>
+        <v>0.270833333333333</v>
       </c>
       <c r="I49" t="n">
-        <v>0.125</v>
+        <v>0.270833333333333</v>
       </c>
       <c r="J49" t="n">
-        <v>0.671641791044776</v>
+        <v>0.417910447761194</v>
       </c>
       <c r="K49" t="n">
-        <v>0.314270833333333</v>
+        <v>0.3065625</v>
       </c>
       <c r="L49" t="n">
-        <v>0.274220838450523</v>
+        <v>0.280741618978883</v>
       </c>
       <c r="M49" t="b">
         <v>0</v>
@@ -4859,19 +4859,19 @@
         <v>23</v>
       </c>
       <c r="H56" t="n">
-        <v>0.0833333333333333</v>
+        <v>0</v>
       </c>
       <c r="I56" t="n">
-        <v>0.0833333333333333</v>
+        <v>0</v>
       </c>
       <c r="J56" t="n">
-        <v>0.835820895522388</v>
+        <v>1</v>
       </c>
       <c r="K56" t="n">
-        <v>0.340729166666667</v>
+        <v>0.343854166666667</v>
       </c>
       <c r="L56" t="n">
-        <v>0.262427517012814</v>
+        <v>0.264200917434386</v>
       </c>
       <c r="M56" t="b">
         <v>0</v>
@@ -5272,19 +5272,19 @@
         <v>23</v>
       </c>
       <c r="H63" t="n">
-        <v>0.142857142857143</v>
+        <v>0</v>
       </c>
       <c r="I63" t="n">
-        <v>0.142857142857143</v>
+        <v>0</v>
       </c>
       <c r="J63" t="n">
-        <v>0.691542288557214</v>
+        <v>1</v>
       </c>
       <c r="K63" t="n">
-        <v>0.310357142857143</v>
+        <v>0.314553571428571</v>
       </c>
       <c r="L63" t="n">
-        <v>0.249432490929981</v>
+        <v>0.247569701372643</v>
       </c>
       <c r="M63" t="b">
         <v>0</v>
@@ -5685,19 +5685,19 @@
         <v>23</v>
       </c>
       <c r="H70" t="n">
-        <v>0.357142857142857</v>
+        <v>0.339285714285714</v>
       </c>
       <c r="I70" t="n">
-        <v>0.357142857142857</v>
+        <v>0.339285714285714</v>
       </c>
       <c r="J70" t="n">
-        <v>0.45273631840796</v>
+        <v>0.427860696517413</v>
       </c>
       <c r="K70" t="n">
-        <v>0.331785714285714</v>
+        <v>0.336517857142857</v>
       </c>
       <c r="L70" t="n">
-        <v>0.254959020517749</v>
+        <v>0.260127755678692</v>
       </c>
       <c r="M70" t="b">
         <v>0</v>
@@ -6098,19 +6098,19 @@
         <v>23</v>
       </c>
       <c r="H77" t="n">
-        <v>0.178571428571429</v>
+        <v>0.0714285714285714</v>
       </c>
       <c r="I77" t="n">
-        <v>0.178571428571429</v>
+        <v>0.0714285714285714</v>
       </c>
       <c r="J77" t="n">
-        <v>0.621890547263682</v>
+        <v>0.875621890547264</v>
       </c>
       <c r="K77" t="n">
-        <v>0.333303571428571</v>
+        <v>0.345625</v>
       </c>
       <c r="L77" t="n">
-        <v>0.264532959351812</v>
+        <v>0.263218981203754</v>
       </c>
       <c r="M77" t="b">
         <v>0</v>
@@ -6511,19 +6511,19 @@
         <v>23</v>
       </c>
       <c r="H84" t="n">
-        <v>0.178571428571429</v>
+        <v>0.357142857142857</v>
       </c>
       <c r="I84" t="n">
-        <v>0.178571428571429</v>
+        <v>0.357142857142857</v>
       </c>
       <c r="J84" t="n">
-        <v>0.671641791044776</v>
+        <v>0.412935323383085</v>
       </c>
       <c r="K84" t="n">
-        <v>0.324821428571429</v>
+        <v>0.326428571428571</v>
       </c>
       <c r="L84" t="n">
-        <v>0.259006009906875</v>
+        <v>0.246950688601508</v>
       </c>
       <c r="M84" t="b">
         <v>0</v>
@@ -6924,19 +6924,19 @@
         <v>23</v>
       </c>
       <c r="H91" t="n">
-        <v>0.0625</v>
+        <v>0</v>
       </c>
       <c r="I91" t="n">
-        <v>0.0625</v>
+        <v>0</v>
       </c>
       <c r="J91" t="n">
-        <v>0.761194029850746</v>
+        <v>1</v>
       </c>
       <c r="K91" t="n">
-        <v>0.2875</v>
+        <v>0.300208333333333</v>
       </c>
       <c r="L91" t="n">
-        <v>0.257943659744636</v>
+        <v>0.242724519323551</v>
       </c>
       <c r="M91" t="b">
         <v>0</v>
@@ -7337,19 +7337,19 @@
         <v>23</v>
       </c>
       <c r="H98" t="n">
-        <v>0.166666666666667</v>
+        <v>0.3125</v>
       </c>
       <c r="I98" t="n">
-        <v>0.166666666666667</v>
+        <v>0.3125</v>
       </c>
       <c r="J98" t="n">
-        <v>0.696517412935323</v>
+        <v>0.442786069651741</v>
       </c>
       <c r="K98" t="n">
-        <v>0.350208333333333</v>
+        <v>0.3275</v>
       </c>
       <c r="L98" t="n">
-        <v>0.263029314650891</v>
+        <v>0.271112309610078</v>
       </c>
       <c r="M98" t="b">
         <v>0</v>
@@ -7750,19 +7750,19 @@
         <v>23</v>
       </c>
       <c r="H105" t="n">
-        <v>0</v>
+        <v>0.145833333333333</v>
       </c>
       <c r="I105" t="n">
-        <v>0</v>
+        <v>0.145833333333333</v>
       </c>
       <c r="J105" t="n">
-        <v>1</v>
+        <v>0.686567164179104</v>
       </c>
       <c r="K105" t="n">
-        <v>0.318958333333333</v>
+        <v>0.330416666666667</v>
       </c>
       <c r="L105" t="n">
-        <v>0.261857529826539</v>
+        <v>0.258036991643433</v>
       </c>
       <c r="M105" t="b">
         <v>0</v>
@@ -8163,19 +8163,19 @@
         <v>23</v>
       </c>
       <c r="H112" t="n">
-        <v>0.232142857142857</v>
+        <v>0.142857142857143</v>
       </c>
       <c r="I112" t="n">
-        <v>0.232142857142857</v>
+        <v>0.142857142857143</v>
       </c>
       <c r="J112" t="n">
-        <v>0.582089552238806</v>
+        <v>0.751243781094527</v>
       </c>
       <c r="K112" t="n">
-        <v>0.323839285714286</v>
+        <v>0.327767857142857</v>
       </c>
       <c r="L112" t="n">
-        <v>0.240024263779417</v>
+        <v>0.230635933318218</v>
       </c>
       <c r="M112" t="b">
         <v>0</v>
@@ -8576,19 +8576,19 @@
         <v>23</v>
       </c>
       <c r="H119" t="n">
-        <v>0.267857142857143</v>
+        <v>0.392857142857143</v>
       </c>
       <c r="I119" t="n">
-        <v>0.267857142857143</v>
+        <v>0.392857142857143</v>
       </c>
       <c r="J119" t="n">
-        <v>0.577114427860697</v>
+        <v>0.378109452736318</v>
       </c>
       <c r="K119" t="n">
-        <v>0.341071428571429</v>
+        <v>0.327142857142857</v>
       </c>
       <c r="L119" t="n">
-        <v>0.254188833105631</v>
+        <v>0.261636672378901</v>
       </c>
       <c r="M119" t="b">
         <v>0</v>
@@ -8989,19 +8989,19 @@
         <v>23</v>
       </c>
       <c r="H126" t="n">
-        <v>0.196428571428571</v>
+        <v>0.285714285714286</v>
       </c>
       <c r="I126" t="n">
-        <v>0.196428571428571</v>
+        <v>0.285714285714286</v>
       </c>
       <c r="J126" t="n">
-        <v>0.666666666666667</v>
+        <v>0.532338308457711</v>
       </c>
       <c r="K126" t="n">
-        <v>0.351428571428571</v>
+        <v>0.354642857142857</v>
       </c>
       <c r="L126" t="n">
-        <v>0.259088713257252</v>
+        <v>0.265070089975714</v>
       </c>
       <c r="M126" t="b">
         <v>0</v>
@@ -9411,10 +9411,10 @@
         <v>1</v>
       </c>
       <c r="K133" t="n">
-        <v>0.333303571428571</v>
+        <v>0.329553571428571</v>
       </c>
       <c r="L133" t="n">
-        <v>0.253217916197242</v>
+        <v>0.250184512338043</v>
       </c>
       <c r="M133" t="b">
         <v>0</v>
@@ -9815,19 +9815,19 @@
         <v>23</v>
       </c>
       <c r="H140" t="n">
-        <v>0.354166666666667</v>
+        <v>0.25</v>
       </c>
       <c r="I140" t="n">
-        <v>0.354166666666667</v>
+        <v>0.25</v>
       </c>
       <c r="J140" t="n">
-        <v>0.462686567164179</v>
+        <v>0.562189054726368</v>
       </c>
       <c r="K140" t="n">
-        <v>0.338645833333333</v>
+        <v>0.332916666666667</v>
       </c>
       <c r="L140" t="n">
-        <v>0.270990302888299</v>
+        <v>0.263539359749836</v>
       </c>
       <c r="M140" t="b">
         <v>0</v>
@@ -10228,19 +10228,19 @@
         <v>23</v>
       </c>
       <c r="H147" t="n">
-        <v>0.583333333333333</v>
+        <v>0.479166666666667</v>
       </c>
       <c r="I147" t="n">
-        <v>0.583333333333333</v>
+        <v>0.479166666666667</v>
       </c>
       <c r="J147" t="n">
-        <v>0.174129353233831</v>
+        <v>0.283582089552239</v>
       </c>
       <c r="K147" t="n">
-        <v>0.313645833333333</v>
+        <v>0.320520833333333</v>
       </c>
       <c r="L147" t="n">
-        <v>0.262853527294459</v>
+        <v>0.263379729993166</v>
       </c>
       <c r="M147" t="b">
         <v>0</v>
@@ -10641,19 +10641,19 @@
         <v>23</v>
       </c>
       <c r="H154" t="n">
-        <v>0.270833333333333</v>
+        <v>0.145833333333333</v>
       </c>
       <c r="I154" t="n">
-        <v>0.270833333333333</v>
+        <v>0.145833333333333</v>
       </c>
       <c r="J154" t="n">
-        <v>0.567164179104478</v>
+        <v>0.73134328358209</v>
       </c>
       <c r="K154" t="n">
-        <v>0.348854166666667</v>
+        <v>0.35125</v>
       </c>
       <c r="L154" t="n">
-        <v>0.261220472211878</v>
+        <v>0.260015729885382</v>
       </c>
       <c r="M154" t="b">
         <v>0</v>
